--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92562164551</v>
+        <v>46157.93071204559</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93071204559</v>
+        <v>46157.93154117613</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93154117613</v>
+        <v>46157.93393863516</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93393863516</v>
+        <v>46157.93708657687</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93708657687</v>
+        <v>46158.2821084811</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2821084811</v>
+        <v>46158.29665994232</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29665994232</v>
+        <v>46158.29805577253</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29805577253</v>
+        <v>46158.33381603689</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33381603689</v>
+        <v>46158.3684836456</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3684836456</v>
+        <v>46158.37281793536</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
